--- a/NECP Scenario/Results/Regional Results/Crete_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/Crete_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.475718379494038E-08</v>
+        <v>5.131694241163799E-08</v>
       </c>
       <c r="C3">
-        <v>4.497176907184973E-08</v>
+        <v>6.661534551795171E-08</v>
       </c>
       <c r="D3">
-        <v>1.675510420919736E-07</v>
+        <v>2.617003909667736E-07</v>
       </c>
       <c r="E3">
-        <v>6.048190528136293E-06</v>
+        <v>0.0404574253565081</v>
       </c>
       <c r="F3">
-        <v>0.8896376651208786</v>
+        <v>0.8221276605546817</v>
       </c>
       <c r="G3">
-        <v>1.29230154484199</v>
+        <v>1.356478108660091</v>
       </c>
       <c r="H3">
-        <v>1.943570638676535</v>
+        <v>2.031607743095364</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.576787460005418</v>
+        <v>1.576787460005844</v>
       </c>
       <c r="C13">
-        <v>1.576787460007451</v>
+        <v>1.576787460008837</v>
       </c>
       <c r="D13">
-        <v>1.576787460012461</v>
+        <v>1.576787460014008</v>
       </c>
       <c r="E13">
-        <v>1.576787460021579</v>
+        <v>1.576787460026504</v>
       </c>
       <c r="F13">
-        <v>1.576787460037648</v>
+        <v>1.576787460046676</v>
       </c>
       <c r="G13">
-        <v>1.576787460068403</v>
+        <v>1.576787460087584</v>
       </c>
       <c r="H13">
-        <v>1.576787460397974</v>
+        <v>1.576787460472617</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1085,19 +1085,19 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>3.178528246399784E-08</v>
+        <v>4.706823165190299E-08</v>
       </c>
       <c r="E24">
-        <v>1.718097796556498E-07</v>
+        <v>2.773397362539844E-07</v>
       </c>
       <c r="F24">
-        <v>0.2649199547435091</v>
+        <v>0.5323406766176483</v>
       </c>
       <c r="G24">
-        <v>0.6772689362653579</v>
+        <v>0.8633528478960943</v>
       </c>
       <c r="H24">
-        <v>0.8697695574812737</v>
+        <v>0.9949654163481972</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.967314908815698</v>
+        <v>0.8707453836851211</v>
       </c>
       <c r="E27">
-        <v>1.160900372644719</v>
+        <v>1.146164498122682</v>
       </c>
       <c r="F27">
-        <v>2.027912123536691</v>
+        <v>1.828572252863448</v>
       </c>
       <c r="G27">
-        <v>2.678310795219867</v>
+        <v>2.449530555600206</v>
       </c>
       <c r="H27">
-        <v>3.210859694470442</v>
+        <v>3.210859655515777</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0.1357120122818924</v>
+        <v>0.3798338524583262</v>
       </c>
       <c r="E29">
-        <v>0.5133336763543861</v>
+        <v>0.6330264399464376</v>
       </c>
       <c r="F29">
-        <v>0.656202096624552</v>
+        <v>0.6562020966263048</v>
       </c>
       <c r="G29">
-        <v>0.656202096821954</v>
+        <v>0.6562020968019117</v>
       </c>
       <c r="H29">
-        <v>0.656202096921518</v>
+        <v>0.656202096911045</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1267,19 +1267,19 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>8.256735972670382E-09</v>
+        <v>1.23042300128533E-08</v>
       </c>
       <c r="E31">
-        <v>1.362294724526548E-08</v>
+        <v>2.076215326879446E-08</v>
       </c>
       <c r="F31">
-        <v>2.055430349260458E-08</v>
+        <v>3.144169359251619E-08</v>
       </c>
       <c r="G31">
-        <v>2.914335446642598E-08</v>
+        <v>4.414045464369091E-08</v>
       </c>
       <c r="H31">
-        <v>1.726248557296334E-07</v>
+        <v>2.638364082289388E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1.274948954214054</v>
+        <v>1.146188603816564</v>
       </c>
       <c r="E33">
-        <v>1.809510043767038</v>
+        <v>1.651381422153585</v>
       </c>
       <c r="F33">
-        <v>1.809510043878508</v>
+        <v>1.651381422291258</v>
       </c>
       <c r="G33">
-        <v>1.809510043993997</v>
+        <v>1.65138142244337</v>
       </c>
       <c r="H33">
-        <v>1.809510044658165</v>
+        <v>1.651381423239129</v>
       </c>
     </row>
     <row r="34" spans="1:8">
